--- a/excel/Batch_07_Leads_Tracker.xlsx
+++ b/excel/Batch_07_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>

--- a/excel/Batch_07_Leads_Tracker.xlsx
+++ b/excel/Batch_07_Leads_Tracker.xlsx
@@ -767,10 +767,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H5" t="str">
-        <v>Sent</v>
+        <v>Draft</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-09-14</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v>Following up on the EVP Electrical Ltd website concept</v>
@@ -1277,10 +1277,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H11" t="str">
-        <v>Sent</v>
+        <v>Draft</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-09-14</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v>Following up on the Pizza Pazzo website concept</v>
@@ -2183,7 +2183,7 @@
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
-      <formula1>"Draft,Sent,Replied,Closed"</formula1>
+      <formula1>"Draft,Sent,Replied,Mail Not Found,Bounce Back,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>

--- a/excel/Batch_07_Leads_Tracker.xlsx
+++ b/excel/Batch_07_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="200" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1170,7 +1170,7 @@
         <v>07421 186356</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>[x] WhatsApp: 07421 186356</v>
       </c>
       <c r="F10" t="str">
         <v>A practical homepage redesign for ECU Mobile Mechanic</v>

--- a/excel/Batch_07_Leads_Tracker.xlsx
+++ b/excel/Batch_07_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -767,10 +767,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H5" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="J5" t="str">
         <v>Following up on the EVP Electrical Ltd website concept</v>
@@ -1022,10 +1022,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H8" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="J8" t="str">
         <v>Following up on the P&amp;J Martins Services website concept</v>
@@ -1277,10 +1277,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H11" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="J11" t="str">
         <v>Following up on the Pizza Pazzo website concept</v>

--- a/excel/Batch_07_Leads_Tracker.xlsx
+++ b/excel/Batch_07_Leads_Tracker.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -418,6 +418,7 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,9 @@
       </c>
       <c r="R1" t="str">
         <v>Lead Status</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Notes</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -560,6 +564,9 @@
       <c r="R2" t="str">
         <v/>
       </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -645,6 +652,9 @@
       <c r="R3" t="str">
         <v/>
       </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
@@ -730,6 +740,9 @@
       <c r="R4" t="str">
         <v/>
       </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
@@ -815,6 +828,9 @@
       <c r="R5" t="str">
         <v/>
       </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
@@ -900,6 +916,9 @@
       <c r="R6" t="str">
         <v/>
       </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
@@ -985,6 +1004,9 @@
       <c r="R7" t="str">
         <v/>
       </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
@@ -1070,6 +1092,9 @@
       <c r="R8" t="str">
         <v/>
       </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
@@ -1155,6 +1180,9 @@
       <c r="R9" t="str">
         <v/>
       </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
@@ -1240,6 +1268,9 @@
       <c r="R10" t="str">
         <v>Lost</v>
       </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
@@ -1325,6 +1356,9 @@
       <c r="R11" t="str">
         <v/>
       </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
@@ -1411,6 +1445,9 @@
       <c r="R12" t="str">
         <v/>
       </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
@@ -1496,6 +1533,9 @@
       <c r="R13" t="str">
         <v/>
       </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
@@ -1581,6 +1621,9 @@
       <c r="R14" t="str">
         <v/>
       </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
@@ -1666,6 +1709,9 @@
       <c r="R15" t="str">
         <v/>
       </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
@@ -1751,6 +1797,9 @@
       <c r="R16" t="str">
         <v/>
       </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17" t="str">
@@ -1836,6 +1885,9 @@
       <c r="R17" t="str">
         <v/>
       </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
@@ -1921,6 +1973,9 @@
       <c r="R18" t="str">
         <v/>
       </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
@@ -1958,10 +2013,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H19" t="str">
-        <v>Draft</v>
+        <v>Mail Not Found</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>2026-10-07</v>
       </c>
       <c r="J19" t="str">
         <v>Following up on the Skiinic Lounge website concept</v>
@@ -2004,6 +2059,9 @@
         <v/>
       </c>
       <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v/>
       </c>
     </row>
@@ -2091,6 +2149,9 @@
       <c r="R20" t="str">
         <v/>
       </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21" t="str">
@@ -2176,10 +2237,13 @@
       <c r="R21" t="str">
         <v/>
       </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
